--- a/agent_runs/manjidiwang/episodes/ep28/storyboard_index.xlsx
+++ b/agent_runs/manjidiwang/episodes/ep28/storyboard_index.xlsx
@@ -84,7 +84,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>底牌反转（，总时长：12秒，镜头数：6个）</t>
+          <t>底牌反转</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -132,7 +132,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>特勤破窗压场（，总时长：11秒，镜头数：5个）</t>
+          <t>特勤破窗压场</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -180,7 +180,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>过肩摔终局（，总时长：11秒，镜头数：5个）</t>
+          <t>过肩摔终局</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -228,7 +228,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>协议败局（，总时长：11秒，镜头数：5个）</t>
+          <t>协议败局</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -276,7 +276,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>清算书落定（，总时长：10秒，镜头数：5个）</t>
+          <t>清算书落定</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
